--- a/analysis.xlsx
+++ b/analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raghavkhanal/Desktop/SSH/MYCP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5AFD52-ABC9-FF49-9A05-5BBED1C7267A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E33CCBD-D80D-F74E-8A84-B94A0D9A9CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" activeTab="1" xr2:uid="{7F136E20-2255-FA49-8337-A73A0AE59008}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16260" xr2:uid="{7F136E20-2255-FA49-8337-A73A0AE59008}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="71">
   <si>
     <t>Authors</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>HIC</t>
+  </si>
+  <si>
+    <t>Effect on Health System or Health Service Utilization</t>
   </si>
 </sst>
 </file>
@@ -405,7 +408,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -436,24 +439,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -856,16 +857,16 @@
       <c r="F2" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="15" t="s">
         <v>14</v>
       </c>
       <c r="K2" s="4" t="s">
@@ -887,34 +888,34 @@
       <c r="Q2" s="4"/>
     </row>
     <row r="3" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="3">
         <v>2018</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F3" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="14" t="s">
+      <c r="F3" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="19"/>
+      <c r="I3" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J3" s="17"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
@@ -924,34 +925,34 @@
       <c r="Q3" s="5"/>
     </row>
     <row r="4" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="3">
         <v>2018</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="14" t="s">
+      <c r="F4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="19" t="s">
+      <c r="I4" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4" s="17" t="s">
         <v>22</v>
       </c>
       <c r="K4" s="4"/>
@@ -967,34 +968,34 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="3">
         <v>2015</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="14" t="s">
+      <c r="F5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="17" t="s">
         <v>25</v>
       </c>
       <c r="K5" s="4" t="s">
@@ -1012,34 +1013,34 @@
       <c r="Q5" s="4"/>
     </row>
     <row r="6" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="3">
         <v>2015</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="14" t="s">
+      <c r="F6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="19"/>
+      <c r="I6" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" s="17"/>
       <c r="K6" s="5"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -1049,34 +1050,34 @@
       <c r="Q6" s="4"/>
     </row>
     <row r="7" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="3">
         <v>2015</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="18" t="s">
         <v>30</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="19" t="s">
+      <c r="J7" s="17" t="s">
         <v>33</v>
       </c>
       <c r="K7" s="3" t="s">
@@ -1092,34 +1093,34 @@
       <c r="Q7" s="4"/>
     </row>
     <row r="8" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="3">
         <v>2011</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="18" t="s">
         <v>36</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="14" t="s">
+      <c r="F8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="19" t="s">
+      <c r="J8" s="17" t="s">
         <v>38</v>
       </c>
       <c r="K8" s="3"/>
@@ -1135,34 +1136,34 @@
       <c r="Q8" s="4"/>
     </row>
     <row r="9" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="19">
         <v>2012</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="21" t="s">
+      <c r="F9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="17" t="s">
         <v>42</v>
       </c>
       <c r="K9" s="4" t="s">
@@ -1176,34 +1177,34 @@
       <c r="Q9" s="4"/>
     </row>
     <row r="10" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="20">
         <v>2010</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="21" t="s">
+      <c r="F10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="19" t="s">
+      <c r="J10" s="17" t="s">
         <v>42</v>
       </c>
       <c r="K10" s="4" t="s">
@@ -1217,34 +1218,34 @@
       <c r="Q10" s="4"/>
     </row>
     <row r="11" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="20">
         <v>2008</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="21" t="s">
+      <c r="F11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="19" t="s">
+      <c r="J11" s="17" t="s">
         <v>46</v>
       </c>
       <c r="K11" s="4"/>
@@ -1258,34 +1259,34 @@
       <c r="Q11" s="4"/>
     </row>
     <row r="12" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="20">
         <v>2008</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="21" t="s">
+      <c r="F12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="19"/>
+      <c r="J12" s="17"/>
       <c r="K12" s="5"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -1295,34 +1296,34 @@
       <c r="Q12" s="4"/>
     </row>
     <row r="13" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="20">
         <v>2008</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="22" t="s">
+      <c r="F13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" s="19"/>
+      <c r="I13" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J13" s="17"/>
       <c r="K13" s="5"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
@@ -1355,7 +1356,7 @@
       <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="21" t="s">
         <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1387,368 +1388,368 @@
       <c r="D2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="22" t="s">
         <v>61</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="3">
         <v>2018</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="F3" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="14" t="s">
+      <c r="F3" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="19"/>
+      <c r="J3" s="17"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="3">
         <v>2018</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="14" t="s">
+      <c r="F4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="J4" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="3">
         <v>2015</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="14" t="s">
+      <c r="F5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="3">
         <v>2015</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="14" t="s">
+      <c r="F6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="J6" s="19"/>
+      <c r="J6" s="17"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="3">
         <v>2015</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="19" t="s">
+      <c r="J7" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="3">
         <v>2011</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="14" t="s">
+      <c r="F8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="19" t="s">
+      <c r="J8" s="17" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="19">
         <v>2012</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="21" t="s">
+      <c r="F9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="17" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="20">
         <v>2010</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="21" t="s">
+      <c r="F10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="19" t="s">
+      <c r="J10" s="17" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="20">
         <v>2008</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="21" t="s">
+      <c r="F11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="19" t="s">
+      <c r="J11" s="17" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="20">
         <v>2008</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="21" t="s">
+      <c r="F12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="19"/>
+      <c r="J12" s="17"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="20">
         <v>2008</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="E13" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="22" t="s">
+      <c r="F13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="19"/>
+      <c r="J13" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
